--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_999.xlsx
@@ -3207,7 +3207,7 @@
         <v>126</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>116</v>
